--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2503_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2503_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,92 +666,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS2503-08-06-FG</t>
+          <t>FS2503-06-04-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="C2" t="n">
         <v>0.375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="F2" t="n">
         <v>1.7899</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="I2" t="n">
         <v>0.375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.40625</v>
+        <v>0.34375</v>
       </c>
       <c r="K2" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="L2" t="n">
         <v>45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3595</v>
+        <v>0.297</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3145</v>
+        <v>0.252</v>
       </c>
       <c r="O2" t="n">
         <v>0.052</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2125</v>
+        <v>0.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="U2" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="W2" t="n">
         <v>0.05556</v>
       </c>
       <c r="X2" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0625</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="AD2" t="n">
         <v>0.03383</v>
@@ -766,13 +766,13 @@
         <v>0.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.296</v>
+        <v>0.299</v>
       </c>
       <c r="AK2" t="n">
         <v>0.375</v>
@@ -791,47 +791,563 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>FS2503-06-04-FG</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 1/4-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>FS2503</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L12@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "M LGTH" = "0.74" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; N2@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "N LGTH" = "0.87" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "B THREAD" "1/4-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2503: FSM -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: NPTF -04 bore on 2 Air-Way row(s) in 1 tables: 0.28 x2 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on N LGTH=0.87 vs Air-Way N2=0.86 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5381 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2503-06-04-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>FS2503-06-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS2503-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="L3" t="n">
+        <v>45</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>FS2503-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>FS2503</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-06-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2503-6-6-O = Brennan forged FS2503-06-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5382 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FS2503-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>FS2503-08-06-FG</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="B4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="L4" t="n">
+        <v>45</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>FS2503-08-06-FG</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>FS2503</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>3/8-18 NPTF</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-08-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-08-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>forged (-FG): Air-Way non-forged FF2503-8-6-O = Brennan forged FS2503-08-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5383 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>FS2503-08-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS2503-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="L5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.62775</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>FS2503-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 1 1/4-11 1/2 NPTF x 1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>FS2503</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L12@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "M LGTH" = "1.26" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 559.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; N2@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "N LGTH" = "1.67" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 559.2, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "JJ FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 559.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "B THREAD" "1-1/4-11-1/2" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-20-20-FG col "TUBE O.D." "1-1/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSM -20 bore on 18 Air-Way row(s) in 10 tables: 1.02 x18 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: NPTF -20 bore on 2 Air-Way row(s) in 1 tables: 1.25 x2 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on M LGTH=1.26 vs Air-Way L12=1.28; JJ FLATS=1.625 vs Air-Way S2=1.61 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5389 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2503-20-20-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FS2503-20-20-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2503_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2503_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -666,92 +666,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS2503-06-04-FG</t>
+          <t>FS2503-08-06-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="C2" t="n">
         <v>0.375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.26092</v>
+        <v>0.32823</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4018</v>
+        <v>0.4078</v>
       </c>
       <c r="F2" t="n">
         <v>1.7899</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1582</v>
+        <v>0.1522</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
         <v>0.375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.34375</v>
+        <v>0.40625</v>
       </c>
       <c r="K2" t="n">
-        <v>0.39425</v>
+        <v>0.45725</v>
       </c>
       <c r="L2" t="n">
         <v>45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.297</v>
+        <v>0.3595</v>
       </c>
       <c r="N2" t="n">
-        <v>0.252</v>
+        <v>0.3145</v>
       </c>
       <c r="O2" t="n">
         <v>0.052</v>
       </c>
       <c r="P2" t="n">
-        <v>0.15</v>
+        <v>0.2125</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="S2" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="T2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.52183</v>
+        <v>0.65645</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4018</v>
+        <v>0.4078</v>
       </c>
       <c r="W2" t="n">
         <v>0.05556</v>
       </c>
       <c r="X2" t="n">
-        <v>0.26092</v>
+        <v>0.32823</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.21647</v>
+        <v>0.28378</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="AB2" t="n">
         <v>0.0625</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.39425</v>
+        <v>0.45725</v>
       </c>
       <c r="AD2" t="n">
         <v>0.03383</v>
@@ -766,13 +766,13 @@
         <v>0.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="AI2" t="n">
         <v>0.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.299</v>
+        <v>0.296</v>
       </c>
       <c r="AK2" t="n">
         <v>0.375</v>
@@ -791,12 +791,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>FS2503-06-04-FG</t>
+          <t>FS2503-08-06-FG</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 1/4-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -821,43 +821,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L12@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "M LGTH" = "0.74" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; N2@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "N LGTH" = "0.87" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "B THREAD" "1/4-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2503: FSM -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: NPTF -04 bore on 2 Air-Way row(s) in 1 tables: 0.28 x2 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-08-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on N LGTH=0.87 vs Air-Way N2=0.86 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5381 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2503-06-04-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+          <t>forged (-FG): Air-Way non-forged FF2503-8-6-O = Brennan forged FS2503-08-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5383 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FS2503-06-04-FG</t>
+          <t>FS2503-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FS2503-06-06-FG</t>
+          <t>FS2503-06-04-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="C3" t="n">
         <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="F3" t="n">
         <v>1.7899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="H3" t="n">
         <v>0.74</v>
@@ -887,10 +887,10 @@
         <v>0.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="R3" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
         <v>0.26</v>
@@ -899,22 +899,22 @@
         <v>0.74</v>
       </c>
       <c r="U3" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="W3" t="n">
         <v>0.05556</v>
       </c>
       <c r="X3" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AA3" t="n">
         <v>0.6875</v>
@@ -938,7 +938,7 @@
         <v>0.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0.75</v>
@@ -963,12 +963,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>FS2503-06-06-FG</t>
+          <t>FS2503-06-04-FG</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 1/4-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -993,24 +993,24 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-06-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L12@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "M LGTH" = "0.74" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; N2@DRIVE: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "N LGTH" = "0.87" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - pipe leg tip -&gt; crossing; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; S2HEX@HEX: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 2/2 rows with an Air-Way value agree to rounding; THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_A: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "B THREAD" "1/4-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p8 table ORFS-p008-t02 "FS2503-FG MFS-MP 45 DEG ELBOW" row FS2503-06-04-FG col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS2503: FSM -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan]; D2@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: NPTF -04 bore on 2 Air-Way row(s) in 1 tables: 0.28 x2 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF2503-6-6-O = Brennan forged FS2503-06-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5382 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on N LGTH=0.87 vs Air-Way N2=0.86 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5381 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p8 FS2503-06-04-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>FS2503-06-06-FG</t>
+          <t>FS2503-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FS2503-08-06-FG</t>
+          <t>FS2503-06-06-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1032,31 +1032,31 @@
         <v>0.1522</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="I4" t="n">
         <v>0.375</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40625</v>
+        <v>0.34375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="L4" t="n">
         <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3595</v>
+        <v>0.297</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3145</v>
+        <v>0.252</v>
       </c>
       <c r="O4" t="n">
         <v>0.052</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2125</v>
+        <v>0.15</v>
       </c>
       <c r="Q4" t="n">
         <v>0.41</v>
@@ -1065,10 +1065,10 @@
         <v>0.95</v>
       </c>
       <c r="S4" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="U4" t="n">
         <v>0.65645</v>
@@ -1089,13 +1089,13 @@
         <v>0.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0625</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.45725</v>
+        <v>0.39425</v>
       </c>
       <c r="AD4" t="n">
         <v>0.03383</v>
@@ -1116,7 +1116,7 @@
         <v>0.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.296</v>
+        <v>0.299</v>
       </c>
       <c r="AK4" t="n">
         <v>0.375</v>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>FS2503-08-06-FG</t>
+          <t>FS2503-06-06-FG</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>ORFS 45 deg Male Elbow (male face seal x male pipe), 3/8-18 NPTF x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-08-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-8-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2503 (s28, double-pass 2026-10-15, parts.air-way.com/api/series/28, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p8 FS2503-06-06-FG (ORFS-p008-t02); FORGED part: Air-Way NON-forged row FF2503-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF2503-8-6-O = Brennan forged FS2503-08-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5383 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+          <t>forged (-FG): Air-Way non-forged FF2503-6-6-O = Brennan forged FS2503-06-06-FG p8 on every compared cell (M LGTH ~ L12, N LGTH ~ N2, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2503 is used only where Brennan FS2503-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5382 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FS2503-08-06-FG</t>
+          <t>FS2503-06-06-FG</t>
         </is>
       </c>
     </row>
